--- a/data/curriculum_undergraduate.xlsx
+++ b/data/curriculum_undergraduate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/revelunt/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/revelunt/Library/CloudStorage/Dropbox/0. 학부장 업무/학부홈페이지 개편/홈페이지 개편 시안/INDEX/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CAB048-1D95-FC4F-8DC6-F09938DCE267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58454415-34BE-4D4F-BA79-E62F6F6131B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{21A94480-1307-1043-865D-B691F327BBE6}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="28180" activeTab="1" xr2:uid="{21A94480-1307-1043-865D-B691F327BBE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="246">
   <si>
     <t>종별</t>
   </si>
@@ -515,293 +515,325 @@
     <t>COM3179</t>
   </si>
   <si>
-    <t>온라인저널리즘</t>
-  </si>
-  <si>
     <t>COM3180</t>
+  </si>
+  <si>
+    <t>윤도일</t>
+  </si>
+  <si>
+    <t>COM3181</t>
+  </si>
+  <si>
+    <t>언론의자유</t>
+  </si>
+  <si>
+    <t>COM3182</t>
+  </si>
+  <si>
+    <t>뉴미디어영상제작실습</t>
+  </si>
+  <si>
+    <t>하대석</t>
+  </si>
+  <si>
+    <t>여운혁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COM3183</t>
+  </si>
+  <si>
+    <t>OTT콘텐츠기획및제작</t>
+  </si>
+  <si>
+    <t>민선홍</t>
+  </si>
+  <si>
+    <t>COM3186</t>
+  </si>
+  <si>
+    <t>플랫폼편성</t>
+  </si>
+  <si>
+    <t>COM3187</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>언론학고전강독</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COM4109</t>
+  </si>
+  <si>
+    <t>사이버커뮤니케이션</t>
+  </si>
+  <si>
+    <t>COM4115</t>
+  </si>
+  <si>
+    <t>마케팅커뮤니케이션캠페인</t>
+  </si>
+  <si>
+    <t>COM4118</t>
+  </si>
+  <si>
+    <t>행복커뮤니케이션</t>
+  </si>
+  <si>
+    <t>COM4200</t>
+  </si>
+  <si>
+    <t>소통능력</t>
+  </si>
+  <si>
+    <t>김주환</t>
+  </si>
+  <si>
+    <t>김주환</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COM4202</t>
+  </si>
+  <si>
+    <t>온라인미디어분석</t>
+  </si>
+  <si>
+    <t>이상엽</t>
+  </si>
+  <si>
+    <t>COM4205</t>
+  </si>
+  <si>
+    <t>인공지능프로그래밍입문</t>
+  </si>
+  <si>
+    <t>이상엽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COM4206</t>
+  </si>
+  <si>
+    <t>커뮤니케이션텍스트마이닝</t>
+  </si>
+  <si>
+    <t>COM4207</t>
+  </si>
+  <si>
+    <t>위기관리론</t>
+  </si>
+  <si>
+    <t>COM4214</t>
+  </si>
+  <si>
+    <t>공중캠페인: 이론과실습</t>
+  </si>
+  <si>
+    <t>COM4216</t>
+  </si>
+  <si>
+    <t>휴먼커뮤니케이션</t>
+  </si>
+  <si>
+    <t>COM4217</t>
+  </si>
+  <si>
+    <t>인공지능과커뮤니케이션</t>
+  </si>
+  <si>
+    <t>COM4303</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저널리즘스피치실습</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COM3126</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COM3175</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤영철</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>월</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11-12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>12-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4-5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5-6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6-7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7-8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9-10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>월</t>
+  </si>
+  <si>
+    <t>수</t>
+  </si>
+  <si>
+    <t>미디어글쓰기기초</t>
+  </si>
+  <si>
+    <t>빌110</t>
+  </si>
+  <si>
+    <t>목</t>
+  </si>
+  <si>
+    <t>연211</t>
+  </si>
+  <si>
+    <t>디지털저널리즘실습</t>
+  </si>
+  <si>
+    <t>2026-1</t>
+  </si>
+  <si>
+    <t>고철종</t>
+  </si>
+  <si>
+    <t>금혜성</t>
+  </si>
+  <si>
+    <t>2026-2</t>
+  </si>
+  <si>
+    <t>강태우</t>
+  </si>
+  <si>
+    <t>신의경</t>
+  </si>
+  <si>
+    <t>김동환</t>
+  </si>
+  <si>
+    <t>COM3171</t>
+  </si>
+  <si>
+    <t>미디어와정치</t>
+  </si>
+  <si>
+    <t>디지털기술과저널리즘</t>
   </si>
   <si>
     <t>광고와 미디어 테크놀로지
 (구.디지털시대의광고)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>윤도일</t>
-  </si>
-  <si>
-    <t>COM3181</t>
-  </si>
-  <si>
-    <t>언론의자유</t>
-  </si>
-  <si>
-    <t>COM3182</t>
-  </si>
-  <si>
-    <t>뉴미디어영상제작실습</t>
-  </si>
-  <si>
-    <t>하대석</t>
-  </si>
-  <si>
-    <t>여운혁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>COM3183</t>
-  </si>
-  <si>
-    <t>OTT콘텐츠기획및제작</t>
-  </si>
-  <si>
-    <t>민선홍</t>
-  </si>
-  <si>
-    <t>COM3186</t>
-  </si>
-  <si>
-    <t>플랫폼편성</t>
-  </si>
-  <si>
-    <t>COM3187</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>언론학고전강독</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>COM4109</t>
-  </si>
-  <si>
-    <t>사이버커뮤니케이션</t>
-  </si>
-  <si>
-    <t>COM4115</t>
-  </si>
-  <si>
-    <t>마케팅커뮤니케이션캠페인</t>
-  </si>
-  <si>
-    <t>COM4118</t>
-  </si>
-  <si>
-    <t>행복커뮤니케이션</t>
-  </si>
-  <si>
-    <t>COM4200</t>
-  </si>
-  <si>
-    <t>소통능력</t>
-  </si>
-  <si>
-    <t>김주환</t>
-  </si>
-  <si>
-    <t>김주환</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>COM4202</t>
-  </si>
-  <si>
-    <t>온라인미디어분석</t>
-  </si>
-  <si>
-    <t>이상엽</t>
-  </si>
-  <si>
-    <t>COM4205</t>
-  </si>
-  <si>
-    <t>인공지능프로그래밍입문</t>
-  </si>
-  <si>
-    <t>이상엽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>COM4206</t>
-  </si>
-  <si>
-    <t>커뮤니케이션텍스트마이닝</t>
-  </si>
-  <si>
-    <t>COM4207</t>
-  </si>
-  <si>
-    <t>위기관리론</t>
-  </si>
-  <si>
-    <t>COM4214</t>
-  </si>
-  <si>
-    <t>공중캠페인: 이론과실습</t>
-  </si>
-  <si>
-    <t>COM4216</t>
-  </si>
-  <si>
-    <t>휴먼커뮤니케이션</t>
-  </si>
-  <si>
-    <t>COM4217</t>
-  </si>
-  <si>
-    <t>인공지능과커뮤니케이션</t>
-  </si>
-  <si>
-    <t>COM4303</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>저널리즘스피치실습</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>COM3126</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>COM3175</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>윤영철</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>월</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>디지털기술과저널리즘
+(구.온라인저널리즘)</t>
+  </si>
+  <si>
+    <t>COM4305</t>
+  </si>
+  <si>
+    <t>COM4304</t>
+  </si>
+  <si>
+    <t>생성형AI와거대언어모형</t>
+  </si>
+  <si>
+    <t>과학커뮤니케이션</t>
+  </si>
+  <si>
+    <t>I자A521</t>
+  </si>
+  <si>
+    <t>빌210</t>
+  </si>
+  <si>
+    <t>연112</t>
+  </si>
+  <si>
+    <t>커뮤니케이션테크놀로지의이해</t>
+  </si>
+  <si>
+    <t>연313</t>
+  </si>
+  <si>
+    <t>백N208-1</t>
+  </si>
+  <si>
+    <t>백S504</t>
+  </si>
+  <si>
+    <t>고급영상제작실습</t>
+  </si>
+  <si>
+    <t>미디어테크놀로지와사회변화</t>
+  </si>
+  <si>
+    <t>저널리즘의이해</t>
   </si>
   <si>
     <t>화</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>목</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>금</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>빌103</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>연218</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-11</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>11-12</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>백N208</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>12-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1-2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3-4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4-5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5-6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>6-7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>7-8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>9-10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>월</t>
-  </si>
-  <si>
-    <t>성307</t>
-  </si>
-  <si>
-    <t>수</t>
-  </si>
-  <si>
-    <t>미디어글쓰기기초</t>
-  </si>
-  <si>
-    <t>설득커뮤니케이션</t>
-  </si>
-  <si>
-    <t>빌110</t>
-  </si>
-  <si>
-    <t>목</t>
-  </si>
-  <si>
-    <t>연211</t>
-  </si>
-  <si>
-    <t>동아미디어그룹과함께하는저널리즘의지평</t>
-  </si>
-  <si>
-    <t>디지털저널리즘실습</t>
-  </si>
-  <si>
-    <t>디지털미디어와크리에이터</t>
-  </si>
-  <si>
-    <t>금</t>
-  </si>
-  <si>
-    <t>저널리즘스피치실습</t>
-  </si>
-  <si>
-    <t>2026-1</t>
-  </si>
-  <si>
-    <t>고철종</t>
-  </si>
-  <si>
-    <t>금혜성</t>
-  </si>
-  <si>
-    <t>대별203</t>
-  </si>
-  <si>
-    <t>I진A302</t>
-  </si>
-  <si>
-    <t>외02</t>
+  </si>
+  <si>
+    <t>연410</t>
+  </si>
+  <si>
+    <t>교101</t>
+  </si>
+  <si>
+    <t>백S208</t>
   </si>
 </sst>
 </file>
@@ -811,7 +843,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ "/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -929,6 +961,19 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1311,7 +1356,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1518,24 +1563,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -1548,18 +1575,12 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -1578,20 +1599,56 @@
     <xf numFmtId="49" fontId="16" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2168,8 +2225,12 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47616360-7401-1247-BBB8-2A037B680ECE}" name="표1" displayName="표1" ref="A1:O57" totalsRowShown="0" dataDxfId="14" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47616360-7401-1247-BBB8-2A037B680ECE}" name="표1" displayName="표1" ref="A1:O58" totalsRowShown="0" dataDxfId="14" tableBorderDxfId="13">
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{418175B6-DA01-4449-A0DF-08808457DDB1}" name="종별" dataDxfId="12" dataCellStyle="표준 2 2"/>
     <tableColumn id="2" xr3:uid="{E465CE6E-57B0-E54E-BCE9-2644B041B235}" name="학정번호" dataDxfId="11" dataCellStyle="표준 2 2"/>
@@ -2508,13 +2569,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91807FF8-03B3-1844-BD16-33C96DBD8A94}">
-  <dimension ref="A1:O57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <dimension ref="A1:P60"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="4" max="4" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18">
+    <row r="1" spans="1:16" ht="18">
       <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
@@ -2558,10 +2619,13 @@
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+        <v>216</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="41" t="s">
         <v>14</v>
       </c>
@@ -2581,7 +2645,7 @@
         <v>18</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>20</v>
@@ -2607,8 +2671,11 @@
       <c r="O2" s="12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="41" t="s">
         <v>14</v>
       </c>
@@ -2650,10 +2717,13 @@
         <v>32</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>23</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="42" t="s">
         <v>34</v>
       </c>
@@ -2686,9 +2756,12 @@
         <v>38</v>
       </c>
       <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-    </row>
-    <row r="5" spans="1:15" ht="30">
+      <c r="O4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" s="16"/>
+    </row>
+    <row r="5" spans="1:16" ht="30">
       <c r="A5" s="43" t="s">
         <v>25</v>
       </c>
@@ -2716,8 +2789,11 @@
         <v>41</v>
       </c>
       <c r="O5" s="16"/>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="P5" s="18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="42" t="s">
         <v>34</v>
       </c>
@@ -2755,8 +2831,11 @@
         <v>46</v>
       </c>
       <c r="O6" s="16"/>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6" s="10" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="43" t="s">
         <v>25</v>
       </c>
@@ -2802,8 +2881,11 @@
       <c r="O7" s="11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="P7" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="44" t="s">
         <v>25</v>
       </c>
@@ -2837,8 +2919,9 @@
       <c r="O8" s="11" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="29" customHeight="1">
+      <c r="P8" s="16"/>
+    </row>
+    <row r="9" spans="1:16" ht="29" customHeight="1">
       <c r="A9" s="43" t="s">
         <v>25</v>
       </c>
@@ -2868,8 +2951,11 @@
       <c r="O9" s="11" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="P9" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="42" t="s">
         <v>34</v>
       </c>
@@ -2909,8 +2995,11 @@
       <c r="O10" s="11" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="P10" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="43" t="s">
         <v>25</v>
       </c>
@@ -2946,8 +3035,11 @@
       <c r="O11" s="11" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="P11" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="43" t="s">
         <v>25</v>
       </c>
@@ -2993,8 +3085,11 @@
       <c r="O12" s="11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="P12" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="45" t="s">
         <v>34</v>
       </c>
@@ -3038,8 +3133,9 @@
       <c r="O13" s="12" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="P13" s="16"/>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="44" t="s">
         <v>25</v>
       </c>
@@ -3075,8 +3171,9 @@
       <c r="O14" s="11" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" ht="34" customHeight="1">
+      <c r="P14" s="16"/>
+    </row>
+    <row r="15" spans="1:16" ht="34" customHeight="1">
       <c r="A15" s="45" t="s">
         <v>34</v>
       </c>
@@ -3106,8 +3203,11 @@
         <v>18</v>
       </c>
       <c r="O15" s="16"/>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="P15" s="32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="43" t="s">
         <v>25</v>
       </c>
@@ -3133,8 +3233,11 @@
         <v>78</v>
       </c>
       <c r="O16" s="16"/>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="P16" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="43" t="s">
         <v>25</v>
       </c>
@@ -3172,8 +3275,9 @@
       <c r="O17" s="11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" ht="30">
+      <c r="P17" s="16"/>
+    </row>
+    <row r="18" spans="1:16" ht="30">
       <c r="A18" s="45" t="s">
         <v>34</v>
       </c>
@@ -3207,8 +3311,11 @@
         <v>22</v>
       </c>
       <c r="O18" s="16"/>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="P18" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="43" t="s">
         <v>25</v>
       </c>
@@ -3238,10 +3345,11 @@
       </c>
       <c r="N19" s="16"/>
       <c r="O19" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>22</v>
+      </c>
+      <c r="P19" s="16"/>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="44" t="s">
         <v>25</v>
       </c>
@@ -3271,13 +3379,14 @@
       </c>
       <c r="N20" s="16"/>
       <c r="O20" s="16"/>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="P20" s="16"/>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C21" s="20">
         <v>3</v>
@@ -3304,8 +3413,11 @@
         <v>73</v>
       </c>
       <c r="O21" s="16"/>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="P21" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="42" t="s">
         <v>34</v>
       </c>
@@ -3339,8 +3451,9 @@
       </c>
       <c r="N22" s="34"/>
       <c r="O22" s="16"/>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="P22" s="34"/>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="44" t="s">
         <v>25</v>
       </c>
@@ -3370,8 +3483,11 @@
         <v>101</v>
       </c>
       <c r="O23" s="16"/>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="P23" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="44" t="s">
         <v>25</v>
       </c>
@@ -3399,8 +3515,9 @@
       <c r="M24" s="16"/>
       <c r="N24" s="16"/>
       <c r="O24" s="16"/>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="P24" s="16"/>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="43" t="s">
         <v>25</v>
       </c>
@@ -3434,8 +3551,11 @@
         <v>108</v>
       </c>
       <c r="O25" s="16"/>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="P25" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="44" t="s">
         <v>25</v>
       </c>
@@ -3469,8 +3589,9 @@
       <c r="O26" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="P26" s="16"/>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="45" t="s">
         <v>34</v>
       </c>
@@ -3500,8 +3621,9 @@
       <c r="M27" s="16"/>
       <c r="N27" s="16"/>
       <c r="O27" s="16"/>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="P27" s="16"/>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" s="43" t="s">
         <v>25</v>
       </c>
@@ -3533,8 +3655,11 @@
         <v>24</v>
       </c>
       <c r="O28" s="16"/>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="P28" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" s="44" t="s">
         <v>25</v>
       </c>
@@ -3566,8 +3691,9 @@
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
       <c r="O29" s="16"/>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="P29" s="16"/>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" s="44" t="s">
         <v>25</v>
       </c>
@@ -3599,8 +3725,11 @@
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
       <c r="O30" s="16"/>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="P30" s="11" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" s="43" t="s">
         <v>25</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="O31" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="P31" s="16"/>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" s="44" t="s">
         <v>25</v>
       </c>
@@ -3671,8 +3801,11 @@
         <v>126</v>
       </c>
       <c r="O32" s="16"/>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="P32" s="11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" s="44" t="s">
         <v>25</v>
       </c>
@@ -3706,8 +3839,11 @@
         <v>132</v>
       </c>
       <c r="O33" s="16"/>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="P33" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" s="44" t="s">
         <v>25</v>
       </c>
@@ -3735,8 +3871,9 @@
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
       <c r="O34" s="16"/>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="P34" s="16"/>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" s="44" t="s">
         <v>25</v>
       </c>
@@ -3770,707 +3907,828 @@
       <c r="O35" s="18" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="36" spans="1:15">
-      <c r="A36" s="43" t="s">
+      <c r="P35" s="16"/>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="C36" s="14">
-        <v>3</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>140</v>
+      <c r="B36" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" s="20">
+        <v>3</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>224</v>
       </c>
       <c r="E36" s="22"/>
-      <c r="F36" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G36" s="16"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
       <c r="H36" s="16"/>
       <c r="I36" s="22"/>
-      <c r="J36" s="11" t="s">
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" s="22"/>
+      <c r="N36" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="O36" s="22"/>
+      <c r="P36" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C37" s="14">
+        <v>3</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="E37" s="22"/>
+      <c r="F37" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="K36" s="22"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-    </row>
-    <row r="37" spans="1:15">
-      <c r="A37" s="46" t="s">
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="K37" s="22"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="35" t="s">
+      <c r="B38" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="C37" s="27">
-        <v>3</v>
-      </c>
-      <c r="D37" s="36" t="s">
+      <c r="C38" s="27">
+        <v>3</v>
+      </c>
+      <c r="D38" s="36" t="s">
         <v>142</v>
-      </c>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="H37" s="16"/>
-      <c r="I37" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J37" s="16"/>
-      <c r="K37" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="L37" s="16"/>
-      <c r="M37" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="N37" s="16"/>
-      <c r="O37" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
-      <c r="A38" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="C38" s="14">
-        <v>3</v>
-      </c>
-      <c r="D38" s="30" t="s">
-        <v>144</v>
       </c>
       <c r="E38" s="16"/>
       <c r="F38" s="16"/>
       <c r="G38" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>65</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="H38" s="16"/>
       <c r="I38" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="J38" s="16"/>
       <c r="K38" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="L38" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="M38" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="N38" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="O38" s="12" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+        <v>132</v>
+      </c>
+      <c r="L38" s="16"/>
+      <c r="M38" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="N38" s="16"/>
+      <c r="O38" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="P38" s="16"/>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B39" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="C39" s="24">
-        <v>3</v>
-      </c>
-      <c r="D39" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="16"/>
+      <c r="B39" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" s="14">
+        <v>3</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="H39" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="I39" s="22"/>
+        <v>65</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="J39" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="K39" s="22"/>
+        <v>57</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>145</v>
+      </c>
       <c r="L39" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="M39" s="16"/>
-      <c r="N39" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="O39" s="16"/>
-    </row>
-    <row r="40" spans="1:15" ht="30">
+        <v>145</v>
+      </c>
+      <c r="M39" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="O39" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="P39" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="30">
       <c r="A40" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="C40" s="20">
-        <v>3</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>150</v>
+      <c r="B40" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="C40" s="24">
+        <v>3</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>227</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
       <c r="G40" s="16"/>
       <c r="H40" s="11" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="I40" s="22"/>
-      <c r="J40" s="16"/>
+      <c r="J40" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="K40" s="22"/>
       <c r="L40" s="11" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="M40" s="16"/>
-      <c r="N40" s="11" t="s">
-        <v>38</v>
+      <c r="N40" s="10" t="s">
+        <v>136</v>
       </c>
       <c r="O40" s="16"/>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="P40" s="10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="30">
       <c r="A41" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C41" s="20">
         <v>3</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>153</v>
+        <v>226</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
       <c r="G41" s="16"/>
       <c r="H41" s="11" t="s">
-        <v>76</v>
+        <v>149</v>
       </c>
       <c r="I41" s="22"/>
       <c r="J41" s="16"/>
       <c r="K41" s="22"/>
       <c r="L41" s="11" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="M41" s="16"/>
       <c r="N41" s="11" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="O41" s="16"/>
-    </row>
-    <row r="42" spans="1:15">
+      <c r="P41" s="16"/>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C42" s="20">
         <v>3</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
       <c r="G42" s="16"/>
       <c r="H42" s="11" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="I42" s="22"/>
       <c r="J42" s="16"/>
-      <c r="K42" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="L42" s="16"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="11" t="s">
+        <v>77</v>
+      </c>
       <c r="M42" s="16"/>
-      <c r="N42" s="16"/>
+      <c r="N42" s="11" t="s">
+        <v>77</v>
+      </c>
       <c r="O42" s="16"/>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="P42" s="11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C43" s="20">
         <v>3</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="22"/>
       <c r="G43" s="16"/>
       <c r="H43" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="I43" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="K43" s="16"/>
+        <v>154</v>
+      </c>
+      <c r="I43" s="22"/>
+      <c r="J43" s="16"/>
+      <c r="K43" s="18" t="s">
+        <v>155</v>
+      </c>
       <c r="L43" s="16"/>
       <c r="M43" s="16"/>
       <c r="N43" s="16"/>
       <c r="O43" s="16"/>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="P43" s="16"/>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C44" s="20">
         <v>3</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
       <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
+      <c r="H44" s="11" t="s">
+        <v>158</v>
+      </c>
       <c r="I44" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="J44" s="16"/>
-      <c r="K44" s="11" t="s">
-        <v>46</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="K44" s="16"/>
       <c r="L44" s="16"/>
-      <c r="M44" s="11" t="s">
-        <v>46</v>
-      </c>
+      <c r="M44" s="16"/>
       <c r="N44" s="16"/>
-      <c r="O44" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="O44" s="16"/>
+      <c r="P44" s="16"/>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C45" s="20">
         <v>3</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="22"/>
       <c r="G45" s="16"/>
       <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
+      <c r="I45" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="J45" s="16"/>
       <c r="K45" s="11" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="O45" s="16"/>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="M45" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="N45" s="16"/>
+      <c r="O45" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="P45" s="16"/>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C46" s="20">
         <v>3</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E46" s="22"/>
-      <c r="F46" s="18" t="s">
-        <v>21</v>
-      </c>
+      <c r="F46" s="22"/>
       <c r="G46" s="16"/>
-      <c r="H46" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I46" s="22"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
       <c r="J46" s="16"/>
-      <c r="K46" s="22"/>
+      <c r="K46" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="L46" s="16"/>
       <c r="M46" s="16"/>
-      <c r="N46" s="16"/>
+      <c r="N46" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="O46" s="16"/>
-    </row>
-    <row r="47" spans="1:15">
-      <c r="A47" s="43" t="s">
+      <c r="P46" s="16"/>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B47" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="C47" s="14">
-        <v>3</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F47" s="22"/>
-      <c r="G47" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H47" s="16"/>
-      <c r="I47" s="11" t="s">
-        <v>30</v>
-      </c>
+      <c r="B47" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="C47" s="20">
+        <v>3</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="E47" s="22"/>
+      <c r="F47" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47" s="16"/>
+      <c r="H47" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" s="22"/>
       <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
+      <c r="K47" s="22"/>
       <c r="L47" s="16"/>
       <c r="M47" s="16"/>
       <c r="N47" s="16"/>
       <c r="O47" s="16"/>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="P47" s="16"/>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48" s="43" t="s">
         <v>25</v>
       </c>
       <c r="B48" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C48" s="14">
+        <v>3</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="22"/>
+      <c r="G48" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H48" s="16"/>
+      <c r="I48" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C49" s="14">
+        <v>3</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="N49" s="16"/>
+      <c r="O49" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P49" s="16"/>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="C48" s="14">
-        <v>3</v>
-      </c>
-      <c r="D48" s="15" t="s">
+      <c r="C50" s="20">
+        <v>3</v>
+      </c>
+      <c r="D50" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="22"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="N48" s="16"/>
-      <c r="O48" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
-      <c r="A49" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="B49" s="19" t="s">
+      <c r="E50" s="16"/>
+      <c r="F50" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="C49" s="20">
-        <v>3</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="E49" s="16"/>
-      <c r="F49" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="G49" s="16"/>
-      <c r="H49" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="I49" s="22"/>
-      <c r="J49" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="K49" s="22"/>
-      <c r="L49" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="M49" s="16"/>
-      <c r="N49" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="O49" s="16"/>
-    </row>
-    <row r="50" spans="1:15">
-      <c r="A50" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="B50" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="C50" s="24">
-        <v>3</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="F50" s="22"/>
-      <c r="G50" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="H50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="11" t="s">
+        <v>171</v>
+      </c>
       <c r="I50" s="22"/>
       <c r="J50" s="11" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K50" s="22"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="N50" s="16"/>
+      <c r="L50" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="M50" s="16"/>
+      <c r="N50" s="11" t="s">
+        <v>172</v>
+      </c>
       <c r="O50" s="16"/>
-    </row>
-    <row r="51" spans="1:15">
-      <c r="A51" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="C51" s="14">
-        <v>3</v>
-      </c>
-      <c r="D51" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="E51" s="22"/>
+      <c r="P50" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="C51" s="24">
+        <v>3</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>175</v>
+      </c>
       <c r="F51" s="22"/>
-      <c r="G51" s="16"/>
+      <c r="G51" s="11" t="s">
+        <v>175</v>
+      </c>
       <c r="H51" s="16"/>
       <c r="I51" s="22"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="18" t="s">
-        <v>180</v>
-      </c>
+      <c r="J51" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="K51" s="22"/>
       <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
+      <c r="M51" s="11" t="s">
+        <v>175</v>
+      </c>
       <c r="N51" s="16"/>
-      <c r="O51" s="11" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="O51" s="16"/>
+      <c r="P51" s="16"/>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52" s="43" t="s">
         <v>25</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C52" s="14">
         <v>3</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E52" s="22"/>
-      <c r="F52" s="18" t="s">
-        <v>177</v>
-      </c>
+      <c r="F52" s="22"/>
       <c r="G52" s="16"/>
       <c r="H52" s="16"/>
       <c r="I52" s="22"/>
       <c r="J52" s="16"/>
-      <c r="K52" s="22"/>
-      <c r="L52" s="11" t="s">
+      <c r="K52" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="16"/>
+      <c r="O52" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="P52" s="16"/>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C53" s="14">
+        <v>3</v>
+      </c>
+      <c r="D53" s="17" t="s">
         <v>180</v>
-      </c>
-      <c r="M52" s="16"/>
-      <c r="N52" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="O52" s="16"/>
-    </row>
-    <row r="53" spans="1:15">
-      <c r="A53" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="C53" s="20">
-        <v>3</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>184</v>
       </c>
       <c r="E53" s="22"/>
       <c r="F53" s="18" t="s">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="G53" s="16"/>
       <c r="H53" s="16"/>
       <c r="I53" s="22"/>
-      <c r="J53" s="11" t="s">
-        <v>96</v>
-      </c>
+      <c r="J53" s="16"/>
       <c r="K53" s="22"/>
       <c r="L53" s="11" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="M53" s="16"/>
-      <c r="N53" s="16"/>
+      <c r="N53" s="11" t="s">
+        <v>178</v>
+      </c>
       <c r="O53" s="16"/>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="P53" s="16"/>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C54" s="20">
         <v>3</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="F54" s="22"/>
-      <c r="G54" s="11" t="s">
-        <v>117</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="E54" s="22"/>
+      <c r="F54" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="G54" s="16"/>
       <c r="H54" s="16"/>
-      <c r="I54" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="J54" s="16"/>
-      <c r="K54" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="L54" s="16"/>
-      <c r="M54" s="11" t="s">
-        <v>118</v>
-      </c>
+      <c r="I54" s="22"/>
+      <c r="J54" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="K54" s="22"/>
+      <c r="L54" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="M54" s="16"/>
       <c r="N54" s="16"/>
       <c r="O54" s="16"/>
-    </row>
-    <row r="55" spans="1:15">
+      <c r="P54" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
       <c r="A55" s="44" t="s">
         <v>25</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C55" s="20">
         <v>3</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>173</v>
+        <v>117</v>
       </c>
       <c r="F55" s="22"/>
-      <c r="G55" s="16"/>
+      <c r="G55" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="H55" s="16"/>
       <c r="I55" s="11" t="s">
-        <v>173</v>
+        <v>117</v>
       </c>
       <c r="J55" s="16"/>
       <c r="K55" s="11" t="s">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="L55" s="16"/>
       <c r="M55" s="11" t="s">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="N55" s="16"/>
       <c r="O55" s="16"/>
-    </row>
-    <row r="56" spans="1:15">
-      <c r="A56" s="47" t="s">
+      <c r="P55" s="16"/>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B56" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="C56" s="38">
-        <v>3</v>
-      </c>
-      <c r="D56" s="39" t="s">
-        <v>190</v>
-      </c>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
+      <c r="B56" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C56" s="20">
+        <v>3</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="E56" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="F56" s="22"/>
       <c r="G56" s="16"/>
       <c r="H56" s="16"/>
-      <c r="I56" s="22"/>
+      <c r="I56" s="11" t="s">
+        <v>171</v>
+      </c>
       <c r="J56" s="16"/>
-      <c r="K56" s="18" t="s">
+      <c r="K56" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="L56" s="16"/>
+      <c r="M56" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="N56" s="16"/>
+      <c r="O56" s="16"/>
+      <c r="P56" s="16"/>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="C57" s="38">
+        <v>3</v>
+      </c>
+      <c r="D57" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="22"/>
+      <c r="J57" s="16"/>
+      <c r="K57" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="L56" s="16"/>
-      <c r="M56" s="18" t="s">
+      <c r="L57" s="16"/>
+      <c r="M57" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="N56" s="16"/>
-      <c r="O56" s="18" t="s">
+      <c r="N57" s="16"/>
+      <c r="O57" s="18" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="57" spans="1:15">
-      <c r="A57" s="48" t="s">
+      <c r="P57" s="16"/>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="B57" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="C57" s="50">
-        <v>3</v>
-      </c>
-      <c r="D57" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="E57" s="52"/>
-      <c r="F57" s="52"/>
-      <c r="G57" s="53"/>
-      <c r="H57" s="53"/>
-      <c r="I57" s="52"/>
-      <c r="J57" s="53"/>
-      <c r="K57" s="54" t="s">
+      <c r="B58" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="C58" s="50">
+        <v>3</v>
+      </c>
+      <c r="D58" s="51" t="s">
+        <v>190</v>
+      </c>
+      <c r="E58" s="52"/>
+      <c r="F58" s="52"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="53"/>
+      <c r="I58" s="52"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="L57" s="53"/>
-      <c r="M57" s="55" t="s">
+      <c r="L58" s="53"/>
+      <c r="M58" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="N57" s="53"/>
-      <c r="O57" s="55" t="s">
+      <c r="N58" s="53"/>
+      <c r="O58" s="55" t="s">
         <v>101</v>
+      </c>
+      <c r="P58" s="53"/>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" s="49" t="s">
+        <v>229</v>
+      </c>
+      <c r="C59" s="50">
+        <v>3</v>
+      </c>
+      <c r="D59" s="51" t="s">
+        <v>230</v>
+      </c>
+      <c r="E59" s="52"/>
+      <c r="F59" s="52"/>
+      <c r="G59" s="53"/>
+      <c r="H59" s="53"/>
+      <c r="I59" s="52"/>
+      <c r="J59" s="53"/>
+      <c r="K59" s="53"/>
+      <c r="L59" s="53"/>
+      <c r="M59" s="53"/>
+      <c r="N59" s="53"/>
+      <c r="O59" s="53"/>
+      <c r="P59" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" s="49" t="s">
+        <v>228</v>
+      </c>
+      <c r="C60" s="50">
+        <v>3</v>
+      </c>
+      <c r="D60" s="51" t="s">
+        <v>231</v>
+      </c>
+      <c r="E60" s="52"/>
+      <c r="F60" s="52"/>
+      <c r="G60" s="53"/>
+      <c r="H60" s="53"/>
+      <c r="I60" s="52"/>
+      <c r="J60" s="53"/>
+      <c r="K60" s="53"/>
+      <c r="L60" s="53"/>
+      <c r="M60" s="53"/>
+      <c r="N60" s="53"/>
+      <c r="O60" s="53"/>
+      <c r="P60" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -4484,582 +4742,620 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE2FC47-AFC2-5C4D-96AB-ACC05297AD6A}">
-  <dimension ref="A1:U13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:W13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="13" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="56"/>
-    <col min="2" max="2" width="10.83203125" style="58"/>
-    <col min="3" max="16384" width="10.83203125" style="56"/>
+    <col min="1" max="1" width="5.1640625" style="74" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="80" customWidth="1"/>
+    <col min="3" max="4" width="14.83203125" style="80" customWidth="1"/>
+    <col min="5" max="23" width="14.83203125" style="74" customWidth="1"/>
+    <col min="24" max="16384" width="10.83203125" style="74"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="17" thickBot="1">
-      <c r="A1" s="59"/>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61" t="s">
+    <row r="1" spans="1:23" ht="42" customHeight="1" thickBot="1">
+      <c r="A1" s="56"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="E1" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="G1" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1" s="59" t="s">
+        <v>194</v>
+      </c>
+      <c r="J1" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1" s="59" t="s">
+        <v>195</v>
+      </c>
+      <c r="L1" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="M1" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="N1" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="O1" s="59" t="s">
+        <v>196</v>
+      </c>
+      <c r="P1" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q1" s="59" t="s">
+        <v>196</v>
+      </c>
+      <c r="R1" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="S1" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="T1" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="U1" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="V1" s="59" t="s">
+        <v>197</v>
+      </c>
+      <c r="W1" s="59" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="42" customHeight="1" thickBot="1">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57" t="s">
+        <v>232</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>245</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>238</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>234</v>
+      </c>
+      <c r="G2" s="59" t="s">
+        <v>236</v>
+      </c>
+      <c r="H2" s="59" t="s">
+        <v>243</v>
+      </c>
+      <c r="I2" s="59" t="s">
+        <v>233</v>
+      </c>
+      <c r="J2" s="59" t="s">
+        <v>214</v>
+      </c>
+      <c r="K2" s="59" t="s">
+        <v>236</v>
+      </c>
+      <c r="L2" s="59" t="s">
+        <v>233</v>
+      </c>
+      <c r="M2" s="59" t="s">
+        <v>238</v>
+      </c>
+      <c r="N2" s="59" t="s">
+        <v>244</v>
+      </c>
+      <c r="O2" s="58" t="s">
+        <v>234</v>
+      </c>
+      <c r="P2" s="59" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q2" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="R2" s="59" t="s">
+        <v>237</v>
+      </c>
+      <c r="S2" s="59" t="s">
+        <v>214</v>
+      </c>
+      <c r="T2" s="59" t="s">
+        <v>236</v>
+      </c>
+      <c r="U2" s="59" t="s">
+        <v>233</v>
+      </c>
+      <c r="V2" s="84" t="s">
+        <v>236</v>
+      </c>
+      <c r="W2" s="59" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="42" customHeight="1">
+      <c r="A3" s="60">
+        <v>1</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76" t="s">
+        <v>239</v>
+      </c>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="W3" s="76" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="42" customHeight="1">
+      <c r="A4" s="62">
+        <v>2</v>
+      </c>
+      <c r="B4" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="81"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76" t="s">
+        <v>239</v>
+      </c>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76" t="s">
+        <v>240</v>
+      </c>
+      <c r="W4" s="76" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="42" customHeight="1">
+      <c r="A5" s="62">
+        <v>3</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="81"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76" t="s">
+        <v>239</v>
+      </c>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76" t="s">
+        <v>240</v>
+      </c>
+      <c r="W5" s="76" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="42" customHeight="1">
+      <c r="A6" s="62">
+        <v>4</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="C6" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="81"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="76" t="s">
+        <v>230</v>
+      </c>
+      <c r="K6" s="76" t="s">
+        <v>241</v>
+      </c>
+      <c r="L6" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="76"/>
+      <c r="P6" s="76"/>
+      <c r="Q6" s="76"/>
+      <c r="R6" s="76" t="s">
+        <v>239</v>
+      </c>
+      <c r="S6" s="77"/>
+      <c r="T6" s="77" t="s">
+        <v>231</v>
+      </c>
+      <c r="U6" s="77" t="s">
+        <v>130</v>
+      </c>
+      <c r="V6" s="76" t="s">
+        <v>240</v>
+      </c>
+      <c r="W6" s="76"/>
+    </row>
+    <row r="7" spans="1:23" ht="42" customHeight="1">
+      <c r="A7" s="62">
+        <v>5</v>
+      </c>
+      <c r="B7" s="63" t="s">
+        <v>201</v>
+      </c>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="64" t="s">
+        <v>235</v>
+      </c>
+      <c r="G7" s="64" t="s">
+        <v>170</v>
+      </c>
+      <c r="H7" s="64"/>
+      <c r="I7" s="76" t="s">
+        <v>114</v>
+      </c>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77" t="s">
+        <v>231</v>
+      </c>
+      <c r="L7" s="77" t="s">
+        <v>130</v>
+      </c>
+      <c r="M7" s="76"/>
+      <c r="N7" s="76"/>
+      <c r="O7" s="76"/>
+      <c r="P7" s="76" t="s">
         <v>215</v>
       </c>
-      <c r="D1" s="61" t="s">
-        <v>196</v>
-      </c>
-      <c r="E1" s="61" t="s">
+      <c r="Q7" s="76"/>
+      <c r="R7" s="77" t="s">
+        <v>48</v>
+      </c>
+      <c r="S7" s="76" t="s">
+        <v>230</v>
+      </c>
+      <c r="T7" s="76" t="s">
+        <v>241</v>
+      </c>
+      <c r="U7" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="V7" s="76" t="s">
         <v>215</v>
       </c>
-      <c r="F1" s="61" t="s">
+      <c r="W7" s="76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="42" customHeight="1">
+      <c r="A8" s="62">
+        <v>6</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="64" t="s">
+        <v>235</v>
+      </c>
+      <c r="G8" s="64" t="s">
+        <v>170</v>
+      </c>
+      <c r="H8" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="I8" s="76" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" s="77"/>
+      <c r="K8" s="77" t="s">
+        <v>231</v>
+      </c>
+      <c r="L8" s="77" t="s">
+        <v>130</v>
+      </c>
+      <c r="M8" s="76"/>
+      <c r="N8" s="76"/>
+      <c r="O8" s="64" t="s">
+        <v>235</v>
+      </c>
+      <c r="P8" s="64" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q8" s="76"/>
+      <c r="R8" s="77" t="s">
+        <v>48</v>
+      </c>
+      <c r="S8" s="76" t="s">
+        <v>230</v>
+      </c>
+      <c r="T8" s="76" t="s">
+        <v>241</v>
+      </c>
+      <c r="U8" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="V8" s="76" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="61" t="s">
-        <v>197</v>
-      </c>
-      <c r="H1" s="61" t="s">
-        <v>197</v>
-      </c>
-      <c r="I1" s="61" t="s">
-        <v>197</v>
-      </c>
-      <c r="J1" s="61" t="s">
-        <v>198</v>
-      </c>
-      <c r="K1" s="61" t="s">
-        <v>198</v>
-      </c>
-      <c r="L1" s="61" t="s">
-        <v>198</v>
-      </c>
-      <c r="M1" s="61" t="s">
-        <v>217</v>
-      </c>
-      <c r="N1" s="61" t="s">
-        <v>221</v>
-      </c>
-      <c r="O1" s="61" t="s">
-        <v>221</v>
-      </c>
-      <c r="P1" s="61" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q1" s="61" t="s">
-        <v>199</v>
-      </c>
-      <c r="R1" s="61" t="s">
-        <v>200</v>
-      </c>
-      <c r="S1" s="61" t="s">
-        <v>226</v>
-      </c>
-      <c r="T1" s="61" t="s">
-        <v>200</v>
-      </c>
-      <c r="U1" s="61" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="17" thickBot="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="D2" s="65" t="s">
+      <c r="W8" s="76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="42" customHeight="1">
+      <c r="A9" s="62">
+        <v>7</v>
+      </c>
+      <c r="B9" s="63" t="s">
         <v>202</v>
       </c>
-      <c r="E2" s="66" t="s">
-        <v>232</v>
-      </c>
-      <c r="F2" s="66" t="s">
-        <v>216</v>
-      </c>
-      <c r="G2" s="64" t="s">
-        <v>220</v>
-      </c>
-      <c r="H2" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="I2" s="64" t="s">
-        <v>231</v>
-      </c>
-      <c r="J2" s="64" t="s">
-        <v>220</v>
-      </c>
-      <c r="K2" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="L2" s="65" t="s">
-        <v>233</v>
-      </c>
-      <c r="M2" s="66" t="s">
-        <v>216</v>
-      </c>
-      <c r="N2" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="O2" s="65" t="s">
-        <v>222</v>
-      </c>
-      <c r="P2" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q2" s="65" t="s">
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="I9" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="J9" s="76"/>
+      <c r="K9" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="L9" s="76"/>
+      <c r="M9" s="76"/>
+      <c r="N9" s="76" t="s">
+        <v>128</v>
+      </c>
+      <c r="O9" s="76"/>
+      <c r="P9" s="76"/>
+      <c r="Q9" s="76"/>
+      <c r="R9" s="77" t="s">
+        <v>48</v>
+      </c>
+      <c r="S9" s="76"/>
+      <c r="T9" s="77" t="s">
+        <v>82</v>
+      </c>
+      <c r="U9" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="V9" s="76"/>
+      <c r="W9" s="76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="42" customHeight="1">
+      <c r="A10" s="62">
+        <v>8</v>
+      </c>
+      <c r="B10" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="I10" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="J10" s="76"/>
+      <c r="K10" s="76"/>
+      <c r="L10" s="76"/>
+      <c r="M10" s="76"/>
+      <c r="N10" s="76" t="s">
+        <v>128</v>
+      </c>
+      <c r="O10" s="76"/>
+      <c r="P10" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q10" s="76" t="s">
+        <v>99</v>
+      </c>
+      <c r="R10" s="77" t="s">
+        <v>48</v>
+      </c>
+      <c r="S10" s="76"/>
+      <c r="T10" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="U10" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="V10" s="76"/>
+      <c r="W10" s="76"/>
+    </row>
+    <row r="11" spans="1:23" ht="42" customHeight="1">
+      <c r="A11" s="65">
+        <v>9</v>
+      </c>
+      <c r="B11" s="63" t="s">
         <v>205</v>
       </c>
-      <c r="R2" s="64" t="s">
-        <v>201</v>
-      </c>
-      <c r="S2" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="T2" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="U2" s="65" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="36">
-      <c r="A3" s="67">
-        <v>1</v>
-      </c>
-      <c r="B3" s="68" t="s">
-        <v>214</v>
-      </c>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" s="80" t="s">
-        <v>68</v>
-      </c>
-      <c r="R3" s="80"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="80"/>
-    </row>
-    <row r="4" spans="1:21" ht="36">
-      <c r="A4" s="70">
-        <v>2</v>
-      </c>
-      <c r="B4" s="71" t="s">
-        <v>203</v>
-      </c>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="80" t="s">
-        <v>68</v>
-      </c>
-      <c r="R4" s="80" t="s">
-        <v>219</v>
-      </c>
-      <c r="S4" s="80" t="s">
-        <v>170</v>
-      </c>
-      <c r="T4" s="80"/>
-      <c r="U4" s="80"/>
-    </row>
-    <row r="5" spans="1:21" ht="54">
-      <c r="A5" s="70">
-        <v>3</v>
-      </c>
-      <c r="B5" s="71" t="s">
-        <v>204</v>
-      </c>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80" t="s">
-        <v>70</v>
-      </c>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="80" t="s">
-        <v>68</v>
-      </c>
-      <c r="R5" s="80" t="s">
-        <v>219</v>
-      </c>
-      <c r="S5" s="80" t="s">
-        <v>170</v>
-      </c>
-      <c r="T5" s="80" t="s">
-        <v>70</v>
-      </c>
-      <c r="U5" s="80"/>
-    </row>
-    <row r="6" spans="1:21" ht="54">
-      <c r="A6" s="70">
-        <v>4</v>
-      </c>
-      <c r="B6" s="71" t="s">
+      <c r="C11" s="70"/>
+      <c r="D11" s="70" t="s">
+        <v>182</v>
+      </c>
+      <c r="E11" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="J11" s="76"/>
+      <c r="K11" s="76"/>
+      <c r="L11" s="76"/>
+      <c r="M11" s="76"/>
+      <c r="N11" s="76" t="s">
+        <v>128</v>
+      </c>
+      <c r="O11" s="76"/>
+      <c r="P11" s="76"/>
+      <c r="Q11" s="76" t="s">
+        <v>99</v>
+      </c>
+      <c r="R11" s="76"/>
+      <c r="S11" s="76"/>
+      <c r="T11" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="U11" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="V11" s="76"/>
+      <c r="W11" s="76"/>
+    </row>
+    <row r="12" spans="1:23" ht="42" customHeight="1">
+      <c r="A12" s="66">
+        <v>10</v>
+      </c>
+      <c r="B12" s="67" t="s">
         <v>206</v>
       </c>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="80" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="80" t="s">
-        <v>88</v>
-      </c>
-      <c r="H6" s="80" t="s">
-        <v>179</v>
-      </c>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80" t="s">
-        <v>52</v>
-      </c>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="80" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q6" s="80" t="s">
-        <v>68</v>
-      </c>
-      <c r="R6" s="80" t="s">
-        <v>219</v>
-      </c>
-      <c r="S6" s="80" t="s">
-        <v>170</v>
-      </c>
-      <c r="T6" s="80" t="s">
-        <v>70</v>
-      </c>
-      <c r="U6" s="80"/>
-    </row>
-    <row r="7" spans="1:21" ht="54">
-      <c r="A7" s="70">
-        <v>5</v>
-      </c>
-      <c r="B7" s="71" t="s">
+      <c r="C12" s="71"/>
+      <c r="D12" s="70" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="76"/>
+      <c r="K12" s="76"/>
+      <c r="L12" s="76"/>
+      <c r="M12" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="N12" s="76"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="76" t="s">
+        <v>99</v>
+      </c>
+      <c r="R12" s="76"/>
+      <c r="S12" s="76"/>
+      <c r="T12" s="76"/>
+      <c r="U12" s="76"/>
+      <c r="V12" s="76"/>
+      <c r="W12" s="76"/>
+    </row>
+    <row r="13" spans="1:23" ht="42" customHeight="1" thickBot="1">
+      <c r="A13" s="68">
+        <v>11</v>
+      </c>
+      <c r="B13" s="69" t="s">
         <v>207</v>
       </c>
-      <c r="C7" s="72"/>
-      <c r="D7" s="80" t="s">
-        <v>190</v>
-      </c>
-      <c r="E7" s="72"/>
-      <c r="F7" s="80" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80" t="s">
-        <v>142</v>
-      </c>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80" t="s">
-        <v>52</v>
-      </c>
-      <c r="N7" s="80" t="s">
-        <v>88</v>
-      </c>
-      <c r="O7" s="80"/>
-      <c r="P7" s="80" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q7" s="80" t="s">
-        <v>48</v>
-      </c>
-      <c r="R7" s="80"/>
-      <c r="S7" s="80"/>
-      <c r="T7" s="80"/>
-      <c r="U7" s="80" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="54">
-      <c r="A8" s="70">
-        <v>6</v>
-      </c>
-      <c r="B8" s="71" t="s">
-        <v>210</v>
-      </c>
-      <c r="C8" s="80" t="s">
-        <v>224</v>
-      </c>
-      <c r="D8" s="80" t="s">
-        <v>190</v>
-      </c>
-      <c r="E8" s="72"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80" t="s">
-        <v>142</v>
-      </c>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80" t="s">
-        <v>190</v>
-      </c>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
-      <c r="N8" s="80" t="s">
-        <v>88</v>
-      </c>
-      <c r="O8" s="80"/>
-      <c r="P8" s="80" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q8" s="80" t="s">
-        <v>48</v>
-      </c>
-      <c r="R8" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="S8" s="80"/>
-      <c r="T8" s="80"/>
-      <c r="U8" s="80" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="90">
-      <c r="A9" s="70">
-        <v>7</v>
-      </c>
-      <c r="B9" s="71" t="s">
-        <v>208</v>
-      </c>
-      <c r="C9" s="80" t="s">
-        <v>224</v>
-      </c>
-      <c r="D9" s="80" t="s">
-        <v>218</v>
-      </c>
-      <c r="E9" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="80"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="80"/>
-      <c r="J9" s="80" t="s">
-        <v>227</v>
-      </c>
-      <c r="K9" s="80"/>
-      <c r="L9" s="80" t="s">
-        <v>124</v>
-      </c>
-      <c r="M9" s="80"/>
-      <c r="N9" s="80"/>
-      <c r="O9" s="80" t="s">
-        <v>223</v>
-      </c>
-      <c r="P9" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q9" s="80" t="s">
-        <v>48</v>
-      </c>
-      <c r="R9" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="S9" s="80"/>
-      <c r="T9" s="80" t="s">
-        <v>225</v>
-      </c>
-      <c r="U9" s="80" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="90">
-      <c r="A10" s="70">
-        <v>8</v>
-      </c>
-      <c r="B10" s="71" t="s">
-        <v>209</v>
-      </c>
-      <c r="C10" s="80" t="s">
-        <v>224</v>
-      </c>
-      <c r="D10" s="80" t="s">
-        <v>218</v>
-      </c>
-      <c r="E10" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="I10" s="80"/>
-      <c r="J10" s="80" t="s">
-        <v>227</v>
-      </c>
-      <c r="K10" s="80" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" s="80" t="s">
-        <v>124</v>
-      </c>
-      <c r="M10" s="80"/>
-      <c r="N10" s="80"/>
-      <c r="O10" s="80" t="s">
-        <v>223</v>
-      </c>
-      <c r="P10" s="80" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q10" s="80" t="s">
-        <v>48</v>
-      </c>
-      <c r="R10" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="S10" s="80"/>
-      <c r="T10" s="80" t="s">
-        <v>225</v>
-      </c>
-      <c r="U10" s="80"/>
-    </row>
-    <row r="11" spans="1:21" ht="90">
-      <c r="A11" s="73">
-        <v>9</v>
-      </c>
-      <c r="B11" s="71" t="s">
-        <v>211</v>
-      </c>
-      <c r="C11" s="80"/>
-      <c r="D11" s="80" t="s">
-        <v>218</v>
-      </c>
-      <c r="E11" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="I11" s="80" t="s">
-        <v>162</v>
-      </c>
-      <c r="J11" s="80" t="s">
-        <v>227</v>
-      </c>
-      <c r="K11" s="80" t="s">
-        <v>110</v>
-      </c>
-      <c r="L11" s="80" t="s">
-        <v>124</v>
-      </c>
-      <c r="M11" s="80"/>
-      <c r="N11" s="80"/>
-      <c r="O11" s="80" t="s">
-        <v>223</v>
-      </c>
-      <c r="P11" s="80" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q11" s="80"/>
-      <c r="R11" s="80"/>
-      <c r="S11" s="80"/>
-      <c r="T11" s="80" t="s">
-        <v>225</v>
-      </c>
-      <c r="U11" s="80"/>
-    </row>
-    <row r="12" spans="1:21" ht="36">
-      <c r="A12" s="74">
-        <v>10</v>
-      </c>
-      <c r="B12" s="75" t="s">
-        <v>212</v>
-      </c>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="80"/>
-      <c r="G12" s="80"/>
-      <c r="H12" s="80"/>
-      <c r="I12" s="80" t="s">
-        <v>162</v>
-      </c>
-      <c r="J12" s="80"/>
-      <c r="K12" s="80" t="s">
-        <v>110</v>
-      </c>
-      <c r="L12" s="80"/>
-      <c r="M12" s="80"/>
-      <c r="N12" s="80"/>
-      <c r="O12" s="80"/>
-      <c r="P12" s="80"/>
-      <c r="Q12" s="80"/>
-      <c r="R12" s="80"/>
-      <c r="S12" s="80"/>
-      <c r="T12" s="80"/>
-      <c r="U12" s="80"/>
-    </row>
-    <row r="13" spans="1:21" ht="37" thickBot="1">
-      <c r="A13" s="77">
-        <v>11</v>
-      </c>
-      <c r="B13" s="78" t="s">
-        <v>213</v>
-      </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="80" t="s">
-        <v>162</v>
-      </c>
-      <c r="J13" s="80"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="80"/>
-      <c r="M13" s="80"/>
-      <c r="N13" s="80"/>
-      <c r="O13" s="80"/>
-      <c r="P13" s="80"/>
-      <c r="Q13" s="80"/>
-      <c r="R13" s="80"/>
-      <c r="S13" s="80"/>
-      <c r="T13" s="80"/>
-      <c r="U13" s="80"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="76"/>
+      <c r="K13" s="76"/>
+      <c r="L13" s="76"/>
+      <c r="M13" s="83"/>
+      <c r="N13" s="83"/>
+      <c r="O13" s="76"/>
+      <c r="P13" s="76"/>
+      <c r="Q13" s="76"/>
+      <c r="R13" s="76"/>
+      <c r="S13" s="76"/>
+      <c r="T13" s="76"/>
+      <c r="U13" s="76"/>
+      <c r="V13" s="76"/>
+      <c r="W13" s="76"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
